--- a/ksoft_old/docs/records/Carrier_Records_v2.xlsx
+++ b/ksoft_old/docs/records/Carrier_Records_v2.xlsx
@@ -9093,13 +9093,13 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67E5E2F8-2C9F-4E12-B144-BE843711F7AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE11B52B-60FA-470D-9E2F-D83DE20634D6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46F3C959-1431-4028-A7C7-FC2A3F06B024}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E35D474-9DF1-4F65-94BB-0E2344D91EDD}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A425C1C6-8211-4C54-AC6E-7643238F5DB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C68A0023-E471-45DD-AFC3-44B61466DDE3}"/>
 </file>
--- a/ksoft_old/docs/records/Carrier_Records_v2.xlsx
+++ b/ksoft_old/docs/records/Carrier_Records_v2.xlsx
@@ -9093,13 +9093,13 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE11B52B-60FA-470D-9E2F-D83DE20634D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAFA2B4E-6D68-4ADA-A84D-F584D627708F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E35D474-9DF1-4F65-94BB-0E2344D91EDD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39BBB562-6434-49BC-956D-AD444C1D675F}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C68A0023-E471-45DD-AFC3-44B61466DDE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BF6478C-1727-49D7-9869-605F05F78D97}"/>
 </file>
--- a/ksoft_old/docs/records/Carrier_Records_v2.xlsx
+++ b/ksoft_old/docs/records/Carrier_Records_v2.xlsx
@@ -9093,13 +9093,13 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAFA2B4E-6D68-4ADA-A84D-F584D627708F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67E5E2F8-2C9F-4E12-B144-BE843711F7AC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39BBB562-6434-49BC-956D-AD444C1D675F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46F3C959-1431-4028-A7C7-FC2A3F06B024}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BF6478C-1727-49D7-9869-605F05F78D97}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A425C1C6-8211-4C54-AC6E-7643238F5DB9}"/>
 </file>